--- a/bottegart_progetto/output/da_completare_per_editore.xlsx
+++ b/bottegart_progetto/output/da_completare_per_editore.xlsx
@@ -11,12 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Da completare" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifiche" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Da controllare" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Età da decidere" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Riepilogo'!$A$3:$G$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Da completare'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modifiche'!$A$1:$D$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Da controllare'!$A$3:$D$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modifiche'!$A$1:$D$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Da controllare'!$A$3:$D$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Età da decidere'!$A$3:$E$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -545,23 +547,23 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Settenove</t>
+          <t>Minibombo</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
@@ -572,23 +574,23 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Uovonero</t>
+          <t>Settenove</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -599,23 +601,23 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Terre di Mezzo</t>
+          <t>Uovonero</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -626,23 +628,23 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Camelozampa</t>
+          <t>Terre di Mezzo</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -653,23 +655,23 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>La Meridiana</t>
+          <t>Camelozampa</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
@@ -680,23 +682,23 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Gallucci</t>
+          <t>La Meridiana</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
@@ -707,23 +709,23 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Pelledoca</t>
+          <t>Gallucci</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -734,23 +736,23 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Momo Edizioni</t>
+          <t>Pelledoca</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
@@ -761,23 +763,23 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Tunuè</t>
+          <t>Momo Edizioni</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
@@ -788,23 +790,23 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Cronache Ribelli</t>
+          <t>Tunuè</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
@@ -815,23 +817,23 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Dalia Edizioni</t>
+          <t>Cronache Ribelli</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
@@ -842,23 +844,23 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Edizioni Corsare</t>
+          <t>Dalia Edizioni</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
@@ -869,23 +871,23 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Minibombo</t>
+          <t>Edizioni Corsare</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
@@ -1150,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1202,20 +1204,24 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>La Meridiana</t>
+          <t>Camelozampa</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Il mio Afghanistan (CAA)</t>
+          <t>Amici (miniserie A bocca aperta)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Corretto: età</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
+          <t>Corretto: titolo, autore</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>titolo: Amici</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1225,387 +1231,387 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Milagro in CAA</t>
+          <t>Dracula</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Corretto: età</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr"/>
+          <t>Corretto: età, fascia</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>età di lettura IBS (testo in simboli)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Gallucci</t>
+          <t>La Meridiana</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>La casa nella prateria (serie)</t>
+          <t>Il diario di Anna Frank</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Serie sostituita da titoli precisi</t>
+          <t>Corretto: età, fascia</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>La casa nella prateria (vol. 1)</t>
+          <t>età di lettura IBS (testo in simboli)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Minibombo</t>
+          <t>La Meridiana</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Affamato come un lupo – versione in simboli (InBook)</t>
+          <t>Il mio Afghanistan (CAA)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Tolto dal flipbook</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>versione in simboli InBook, non in vendita</t>
-        </is>
-      </c>
+          <t>Corretto: età, fascia</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Minibombo</t>
+          <t>La Meridiana</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Il libro gatto – versione in simboli (InBook)</t>
+          <t>Milagro in CAA</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Tolto dal flipbook</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>versione in simboli InBook, non in vendita</t>
-        </is>
-      </c>
+          <t>Corretto: età, fascia</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Minibombo</t>
+          <t>Gallucci</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Orso, buco! – versione in simboli (InBook)</t>
+          <t>La casa nella prateria (serie)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Tolto dal flipbook</t>
+          <t>Serie sostituita da titoli precisi</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>versione in simboli InBook, non in vendita</t>
+          <t>La casa nella prateria (vol. 1)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Tunuè</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Io non ho paura del lupo</t>
+          <t>Brina (serie)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Corretto: età</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>Corretto: titolo, autore, trama</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>titolo: Brina. L’alba all’orizzonte</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Tunuè</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Non esistono piccoli antifascisti</t>
+          <t>Monster Allergy (serie)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Corretto: età</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
+          <t>Corretto: titolo, autore, trama</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>titolo: Monster Allergy. Collection, vol. 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Nero Latte</t>
+          <t>Tunuè</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>La bottega di Bepo il sarto</t>
+          <t>Investigators (serie)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Tolto dal flipbook</t>
+          <t>Corretto: titolo, autore, trama</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>fuori catalogo</t>
+          <t>titolo: InvestiGators. Due agenti di classe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Lapis</t>
+          <t>Tunuè</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Avventure di Tato e Nanà</t>
+          <t>Strega a modo mio (serie)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Serie sostituita da titoli precisi</t>
+          <t>Corretto: titolo, autore, trama</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Nanà è arrabbiata; Il bacio arcobaleno</t>
+          <t>titolo: Strega a modo mio</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Lapis</t>
+          <t>Tunuè</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>I senza parole di Attilio</t>
+          <t>Le sorelle Grémillet (serie)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Serie sostituita da titoli precisi</t>
+          <t>Corretto: titolo, autore, trama</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Meglio insieme; Pio pio bau bau</t>
+          <t>titolo: Le sorelle Grémillet. La villa dei misteri</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Lapis</t>
+          <t>Dalia Edizioni</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Foto di gruppo (versione in simboli InBook)</t>
+          <t>UVA. Una Vita Altrove</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Tolto dal flipbook</t>
+          <t>Corretto: età</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>versione in simboli InBook, non in vendita</t>
+          <t>indicato “adolescenti” nel catalogo Dalia</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Lapis</t>
+          <t>Minibombo</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Le mini storie di Attilio</t>
+          <t>Affamato come un lupo – versione in simboli (InBook)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Serie sostituita da titoli precisi</t>
+          <t>Tolto dal flipbook</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Cappuccetto Rosso; Vieni a giocare?</t>
+          <t>versione in simboli InBook, non in vendita</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Lapis</t>
+          <t>Minibombo</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Storie di una principessina (Tilly)</t>
+          <t>Il libro gatto – versione in simboli (InBook)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Serie sostituita da titoli precisi</t>
+          <t>Tolto dal flipbook</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Voglio il mio ciuccio; Voglio il mio vasino</t>
+          <t>versione in simboli InBook, non in vendita</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Lapis</t>
+          <t>Minibombo</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Dardo il cane di Leonardo</t>
+          <t>Orso, buco! – versione in simboli (InBook)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Serie sostituita da titoli precisi</t>
+          <t>Tolto dal flipbook</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>La collana di Monna Lisa (Dardo il cane di Leonardo, vol. 1)</t>
+          <t>versione in simboli InBook, non in vendita</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Lapis</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Mabel (prime letture)</t>
+          <t>Io non ho paura del lupo</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Serie sostituita da titoli precisi</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Magnifica Mabel e il disastro del coniglio</t>
-        </is>
-      </c>
+          <t>Corretto: età, fascia</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Lapis</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Omero – Iliade / Odissea per ragazzi</t>
+          <t>Non esistono piccoli antifascisti</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Serie sostituita da titoli precisi</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Iliade; Odissea</t>
-        </is>
-      </c>
+          <t>Corretto: età, fascia</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Lapis</t>
+          <t>Nero Latte</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>I misteri di Teo</t>
+          <t>La bottega di Bepo il sarto</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Serie sostituita da titoli precisi</t>
+          <t>Tolto dal flipbook</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Il segreto del labirinto (I misteri di Teo)</t>
+          <t>fuori catalogo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>effequ</t>
+          <t>Logos</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>XY</t>
+          <t>La Sirenetta</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Corretto: ISBN</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
+          <t>Corretto: età, fascia</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Bottegart chiedeva di abbassare l’età: IBS indica “da 5 anni” (il listino Logos diceva 12)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>BeccoGiallo</t>
+          <t>Lapis</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Adele Crudele (serie)</t>
+          <t>Avventure di Tato e Nanà</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1615,19 +1621,19 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Adele Crudele 1. Tutto questo finirà male</t>
+          <t>Nanà è arrabbiata; Il bacio arcobaleno</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>BeccoGiallo</t>
+          <t>Lapis</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Ariol (serie)</t>
+          <t>I senza parole di Attilio</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1637,7 +1643,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Ariol. Un piccolo asino come te e me</t>
+          <t>Meglio insieme; Pio pio bau bau</t>
         </is>
       </c>
     </row>
@@ -1649,124 +1655,1814 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Versi diversi / Sì, io sono (poesia)</t>
+          <t>Foto di gruppo (versione in simboli InBook)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Serie sostituita da titoli precisi</t>
+          <t>Tolto dal flipbook</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Occhio ladro; Un anno di poesia</t>
+          <t>versione in simboli InBook, non in vendita</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>La Meridiana</t>
+          <t>Lapis</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Cinque racconti brevi con protagonisti adolescenti (collana Parimenti)</t>
+          <t>Le mini storie di Attilio</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Tolto dal flipbook</t>
+          <t>Serie sostituita da titoli precisi</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>è lo stesso libro di “A Said piaceva il mare” (cinque storie di adolescenti, collana Parimenti)</t>
+          <t>Cappuccetto Rosso; Vieni a giocare?</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>BeccoGiallo</t>
+          <t>Lapis</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>L’immigrazione spiegata ai bambini</t>
+          <t>Storie di una principessina (Tilly)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Corretto: autore, ISBN, età</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr"/>
+          <t>Serie sostituita da titoli precisi</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Voglio il mio ciuccio; Voglio il mio vasino</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Terre di Mezzo</t>
+          <t>Lapis</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>La grande fabbrica delle parole</t>
+          <t>Dardo il cane di Leonardo</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Corretto: ISBN</t>
+          <t>Serie sostituita da titoli precisi</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>ISBN aggiornato all’edizione a colori in commercio (prezzo 18,00 €)</t>
+          <t>La collana di Monna Lisa (Dardo il cane di Leonardo, vol. 1)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>La Meridiana</t>
+          <t>Lapis</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Piccole donne</t>
+          <t>Mabel (prime letture)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Corretto: ISBN, prezzo</t>
+          <t>Serie sostituita da titoli precisi</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>nel catalogo c’era il prezzo scontato IBS (15,20 €); il prezzo di copertina è 16,00 €</t>
+          <t>Magnifica Mabel e il disastro del coniglio</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>Lapis</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Omero – Iliade / Odissea per ragazzi</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Serie sostituita da titoli precisi</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Iliade; Odissea</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Lapis</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>I misteri di Teo</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Serie sostituita da titoli precisi</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Il segreto del labirinto (I misteri di Teo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Le cronache dell’acero e del ciliegio (4 libri)</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: titolo, autore, trama</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>titolo: Le cronache dell’acero e del ciliegio 1. La maschera di Nō</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>effequ</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>XY</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: ISBN</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Adele Crudele (serie)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Serie sostituita da titoli precisi</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Adele Crudele 1. Tutto questo finirà male</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Ariol (serie)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Serie sostituita da titoli precisi</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Ariol. Un piccolo asino come te e me</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Lapis</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Versi diversi / Sì, io sono (poesia)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Serie sostituita da titoli precisi</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Occhio ladro; Un anno di poesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>La Meridiana</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Cinque racconti brevi con protagonisti adolescenti (collana Parimenti)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Tolto dal flipbook</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>è lo stesso libro di “A Said piaceva il mare” (cinque storie di adolescenti, collana Parimenti)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>L’immigrazione spiegata ai bambini</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: autore, ISBN, età, fascia</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>La grande fabbrica delle parole</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: ISBN</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>ISBN aggiornato all’edizione a colori in commercio (prezzo 18,00 €)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>La Meridiana</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Piccole donne</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: ISBN, età, prezzo</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>nel catalogo c’era il prezzo scontato IBS (15,20 €); il prezzo di copertina è 16,00 €; coerente con la fascia 9+ scelta da Bottegart</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>Momo Edizioni</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Karukinka. La nostra terra</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: età, fascia</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Edizioni Corsare</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Wonder Football Club (serie)</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: titolo, autore, trama</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>titolo: Wonder Football Club 1. Fare squadra</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Anatomia / Oceano / Nascita / Mondo vegetale (libri animati)</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: titolo, autore, trama</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>titolo: Anatomia</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Esplorando l’universo / Esplorando gli elementi</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: titolo, autore, trama</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>titolo: Esplorando l’universo</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Enciclopedia del Meraviglioso (I draghi, Le streghe, I fantasmi...)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: titolo, autore, età, trama</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>titolo: Sirene, centauri e altre chimere (L’enciclopedia del meraviglioso); nel catalogo L’Ippocampo è nella sezione Scuole medie; IBS indica “da 5 anni”, da verificare</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Le streghe di Venezia (3 volumi)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: titolo, autore, età, trama</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>titolo: Le streghe di Venezia; nel catalogo L’Ippocampo è nella narrativa ragazzi; IBS indica “da 7 anni” ma la protagonista ha 16 anni: da verificare</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Il ministero delle Soluzioni</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: età, fascia</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>età di lettura IBS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Corpo a corpo</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Corretto: età</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>collana Young Adult di Terre di Mezzo, fascia Adolescenza</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>L’eterno ritorno di Clara hart</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: età</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>collana Young Adult di Terre di Mezzo, fascia Adolescenza</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Poi prenderemo New York</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: età</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>collana Young Adult di Terre di Mezzo, fascia Adolescenza</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Un ragazzo è quasi niente</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Corretto: età</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>collana Young Adult di Terre di Mezzo, fascia Adolescenza</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Il segreto di Ella</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>fascia: 10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Jane negli abissi</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 11 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Provaci ancora, Selma!</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>fascia: 10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Sotto la stessa luna</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 11 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Il gruppo</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>autore: Kari Stai</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Quell’estate con Yente</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>autore: Enne Koens</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>La Meridiana</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Il mio Afghanistan (CAA)</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>autore: G. Najafi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>La Meridiana</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Milagro in CAA</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>autore: A. Bello</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Adele Crudele 1. Tutto questo finirà male</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>fascia: 10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Senza titolo</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>autore: Erna Sassen</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Vulcano</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>autore: Zakiya Ajmi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Tunuè</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Angelica e il principe orso (in arrivo)</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>titolo: Angelica e il principe orso; autore: Trung Le Nguyen</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>La Meridiana</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Piccole donne</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>fascia: 9+</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Tunuè</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>L’Attraversaspecchi, vol. 1 – Fidanzati dell’inverno</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>autore: Christelle Dabos</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Tunuè</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Noi due</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>autore: Sara Soler</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Alfonsina corre</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Celeste e la gemella Blu</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Che cos’è la scuola?</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Che cos’è l’amicizia?</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Cosa fanno i sentimenti di notte?</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>C’è posta per Volpe</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Dall’altra parte del mare</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Di quante persone abbiamo bisogno?</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Il libro dal futuro</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Il nemico</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 6 anni; fascia: Prime letture (6-8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>La grande fabbrica delle parole</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>La libertà del polpo</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>La vera storia della Strega Cattiva</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Le persone sono strane</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Non tutte le principesse</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Ogni viso è una poesia</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Un barattolo di emozioni</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Un posto chiamato casa</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Un posto nel cuore del maestro Orso Bruno</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Terre di Mezzo</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Fratelli</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Avrò cura di te</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>autore: Maria Loretta Giraldo; ill. Nicoletta Bertelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Cielo di ciliegie</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>autore: Jef Aerts; ill. Sanne te Loo</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Dove nasco ogni giorno</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>autore: Arianna Papini</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Felicità è una parola semplice</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>autore: Arianna Papini</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Il cortile selvaggio</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>autore: Anne-Hélène Dubray; ill. Sarah Loulendo</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Il giardino di Rita</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>autore: Michelangelo Rossato; ill. Francesca Corso</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>La sorpresa della volpe</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>autore: Virginia Stefanini; ill. Margherita Micheli</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Gallucci</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Tu sei importante</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>autore: Christian Robinson</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Momo Edizioni</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Bollicina</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>70 trucchi per non fare il bagno</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>autore: Gideon Samson</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Dove sono finiti i bambini?</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>autore: Indrek Koff</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Isidoro e la luna</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>autore: Giorgos Panagiotakis</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>La figlia della biblioteca</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>autore: Polly Horvath; eta: da 10 anni; fascia: 10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>La Meridiana</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Giacomo di cristallo e altre storie</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>eta: da 6 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>La Meridiana</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>La Puglia è una favola</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>autore: Tonio Vinci, Simona Versi; eta: da 6 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Cronache Ribelli</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>C’era una (ri)volta – Quaranta storie da leggere e colorare (vol. I)</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>autore: AA.VV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Cronache Ribelli</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>C’era una (ri)volta – Quaranta storie da leggere e colorare (vol. II)</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>autore: AA.VV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Archeo Tales – Il mito del Minotauro</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>autore: Emanuele Apostolidis, Francesco Bellu, Federico Gardin</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>La disabilità spiegata ai bambini e alle bambine</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>autore: Marina Cuollo; ill. Cristina Trapanese</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Le emozioni spiegate alle bambine e ai bambini</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>autore: Lorenzo Stivano, Ludovica Sodano</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Woman Power</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Correzione Bottegart</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>titolo: Woman Power. Donne che hanno cambiato il mondo; autore: Rebecca June, Ximo Abadia</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D29"/>
+  <autoFilter ref="A1:D106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1777,7 +3473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2985,7 +4681,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Fratelli</t>
+          <t>Il ministero delle Soluzioni</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -2993,11 +4689,7 @@
           <t>età</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ibs.it/x/e/9791259962942</t>
-        </is>
-      </c>
+      <c r="D57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -3007,7 +4699,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Il mondo è tuo</t>
+          <t>Corpo a corpo</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3015,11 +4707,7 @@
           <t>età</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ibs.it/x/e/9788861893740</t>
-        </is>
-      </c>
+      <c r="D58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -3029,7 +4717,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Via della gentilezza</t>
+          <t>L’eterno ritorno di Clara hart</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3037,119 +4725,107 @@
           <t>età</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ibs.it/x/e/9788861897595</t>
-        </is>
-      </c>
+      <c r="D59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Camelozampa</t>
+          <t>Terre di Mezzo</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Amici (miniserie A bocca aperta)</t>
+          <t>Poi prenderemo New York</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>trama</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ibs.it/x/e/9791280014214</t>
-        </is>
-      </c>
+          <t>età</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Camelozampa</t>
+          <t>Terre di Mezzo</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Peggy trova tutto</t>
+          <t>Un ragazzo è quasi niente</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>ISBN</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ibs.it/x/e/9791254642351</t>
-        </is>
-      </c>
+          <t>età</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Camelozampa</t>
+          <t>Terre di Mezzo</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Avrò cura di te</t>
+          <t>Fratelli</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>trama</t>
+          <t>età</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791280014139</t>
+          <t>https://www.ibs.it/x/e/9791259962942</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Camelozampa</t>
+          <t>Terre di Mezzo</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Cielo di ciliegie</t>
+          <t>Il mondo è tuo</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>trama</t>
+          <t>età</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254641590</t>
+          <t>https://www.ibs.it/x/e/9788861893740</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Camelozampa</t>
+          <t>Terre di Mezzo</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Dove nasco ogni giorno</t>
+          <t>Via della gentilezza</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>ISBN</t>
+          <t>età</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642542</t>
+          <t>https://www.ibs.it/x/e/9788861897595</t>
         </is>
       </c>
     </row>
@@ -3161,17 +4837,17 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Felicità è una parola semplice</t>
+          <t>Peggy trova tutto</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>trama</t>
+          <t>ISBN</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791280014382</t>
+          <t>https://www.ibs.it/x/e/9791254642351</t>
         </is>
       </c>
     </row>
@@ -3183,17 +4859,17 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Il cortile selvaggio</t>
+          <t>Avrò cura di te</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>ISBN</t>
+          <t>trama</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642863</t>
+          <t>https://www.ibs.it/x/e/9791280014139</t>
         </is>
       </c>
     </row>
@@ -3205,17 +4881,17 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Il giardino di Rita</t>
+          <t>Cielo di ciliegie</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>ISBN</t>
+          <t>trama</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642146</t>
+          <t>https://www.ibs.it/x/e/9791254641590</t>
         </is>
       </c>
     </row>
@@ -3227,17 +4903,17 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>La sorpresa della volpe</t>
+          <t>Dove nasco ogni giorno</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>trama</t>
+          <t>ISBN</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788899842888</t>
+          <t>https://www.ibs.it/x/e/9791254642542</t>
         </is>
       </c>
     </row>
@@ -3249,17 +4925,17 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>70 trucchi per non fare il bagno</t>
+          <t>Felicità è una parola semplice</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>ISBN</t>
+          <t>trama</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642917</t>
+          <t>https://www.ibs.it/x/e/9791280014382</t>
         </is>
       </c>
     </row>
@@ -3271,7 +4947,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Dove sono finiti i bambini?</t>
+          <t>Il cortile selvaggio</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3281,7 +4957,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642047</t>
+          <t>https://www.ibs.it/x/e/9791254642863</t>
         </is>
       </c>
     </row>
@@ -3293,7 +4969,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Isidoro e la luna</t>
+          <t>Il giardino di Rita</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -3303,7 +4979,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642023</t>
+          <t>https://www.ibs.it/x/e/9791254642146</t>
         </is>
       </c>
     </row>
@@ -3315,17 +4991,17 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>La figlia della biblioteca</t>
+          <t>La sorpresa della volpe</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>ISBN</t>
+          <t>trama</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642764</t>
+          <t>https://www.ibs.it/x/e/9788899842888</t>
         </is>
       </c>
     </row>
@@ -3337,7 +5013,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Furia Mascherata</t>
+          <t>70 trucchi per non fare il bagno</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -3347,7 +5023,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642528</t>
+          <t>https://www.ibs.it/x/e/9791254642917</t>
         </is>
       </c>
     </row>
@@ -3359,17 +5035,17 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>La mia vita imprevista</t>
+          <t>Dove sono finiti i bambini?</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>trama</t>
+          <t>ISBN</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642153</t>
+          <t>https://www.ibs.it/x/e/9791254642047</t>
         </is>
       </c>
     </row>
@@ -3381,7 +5057,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Oggi non si torna a casa</t>
+          <t>Isidoro e la luna</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -3391,7 +5067,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642788</t>
+          <t>https://www.ibs.it/x/e/9791254642023</t>
         </is>
       </c>
     </row>
@@ -3403,7 +5079,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Il gruppo</t>
+          <t>La figlia della biblioteca</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3413,7 +5089,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642689</t>
+          <t>https://www.ibs.it/x/e/9791254642764</t>
         </is>
       </c>
     </row>
@@ -3425,7 +5101,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Quell’estate con Yente</t>
+          <t>Furia Mascherata</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -3435,7 +5111,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254641989</t>
+          <t>https://www.ibs.it/x/e/9791254642528</t>
         </is>
       </c>
     </row>
@@ -3447,17 +5123,17 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Figlia del destino</t>
+          <t>La mia vita imprevista</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>ISBN</t>
+          <t>trama</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254641934</t>
+          <t>https://www.ibs.it/x/e/9791254642153</t>
         </is>
       </c>
     </row>
@@ -3469,7 +5145,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Lemming e fiocchi di neve</t>
+          <t>Oggi non si torna a casa</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -3479,7 +5155,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642030</t>
+          <t>https://www.ibs.it/x/e/9791254642788</t>
         </is>
       </c>
     </row>
@@ -3491,17 +5167,17 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Senza titolo</t>
+          <t>Il gruppo</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>trama</t>
+          <t>ISBN</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254641873</t>
+          <t>https://www.ibs.it/x/e/9791254642689</t>
         </is>
       </c>
     </row>
@@ -3513,7 +5189,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Vulcano</t>
+          <t>Quell’estate con Yente</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -3523,19 +5199,19 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791254642016</t>
+          <t>https://www.ibs.it/x/e/9791254641989</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>La Meridiana</t>
+          <t>Camelozampa</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Dracula</t>
+          <t>Figlia del destino</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3545,19 +5221,19 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788861536579</t>
+          <t>https://www.ibs.it/x/e/9791254641934</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>La Meridiana</t>
+          <t>Camelozampa</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Il diario di Anna Frank</t>
+          <t>Lemming e fiocchi di neve</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -3567,51 +5243,51 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788861536326</t>
+          <t>https://www.ibs.it/x/e/9791254642030</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>La Meridiana</t>
+          <t>Camelozampa</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Piccole donne</t>
+          <t>Senza titolo</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>trama, prezzo, ISBN</t>
+          <t>trama</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791256260539</t>
+          <t>https://www.ibs.it/x/e/9791254641873</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>La Meridiana</t>
+          <t>Camelozampa</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>A Said piaceva il mare</t>
+          <t>Vulcano</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>trama, età, ISBN</t>
+          <t>ISBN</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788861537101</t>
+          <t>https://www.ibs.it/x/e/9791254642016</t>
         </is>
       </c>
     </row>
@@ -3623,7 +5299,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Canto di Natale</t>
+          <t>Dracula</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3633,7 +5309,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788861537200</t>
+          <t>https://www.ibs.it/x/e/9788861536579</t>
         </is>
       </c>
     </row>
@@ -3645,17 +5321,17 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Frida Kahlo pittrice coraggiosa</t>
+          <t>Il diario di Anna Frank</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>trama, età, ISBN</t>
+          <t>età, ISBN</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788861539952</t>
+          <t>https://www.ibs.it/x/e/9788861536326</t>
         </is>
       </c>
     </row>
@@ -3667,17 +5343,17 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Giacomo di cristallo e altre storie</t>
+          <t>Piccole donne</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>trama, età, ISBN</t>
+          <t>trama, età, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788861537958</t>
+          <t>https://www.ibs.it/x/e/9791256260539</t>
         </is>
       </c>
     </row>
@@ -3689,7 +5365,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Il mio Afghanistan (CAA)</t>
+          <t>A Said piaceva il mare</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -3699,7 +5375,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788861538955 · età indicata da Bottegart</t>
+          <t>https://www.ibs.it/x/e/9788861537101</t>
         </is>
       </c>
     </row>
@@ -3711,17 +5387,17 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>L’albero del riccio</t>
+          <t>Canto di Natale</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>trama, età, ISBN</t>
+          <t>età, ISBN</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788861539808</t>
+          <t>https://www.ibs.it/x/e/9788861537200</t>
         </is>
       </c>
     </row>
@@ -3733,7 +5409,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>La Puglia è una favola</t>
+          <t>Frida Kahlo pittrice coraggiosa</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -3743,7 +5419,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791256260089</t>
+          <t>https://www.ibs.it/x/e/9788861539952</t>
         </is>
       </c>
     </row>
@@ -3755,7 +5431,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Milagro in CAA</t>
+          <t>Giacomo di cristallo e altre storie</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3765,7 +5441,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788861539983 · età indicata da Bottegart</t>
+          <t>https://www.ibs.it/x/e/9788861537958</t>
         </is>
       </c>
     </row>
@@ -3777,7 +5453,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Paul Klee pittore musicista</t>
+          <t>Il mio Afghanistan (CAA)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -3787,183 +5463,183 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791256260560</t>
+          <t>https://www.ibs.it/x/e/9788861538955 · età indicata da Bottegart</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Gallucci</t>
+          <t>La Meridiana</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Il mondo di Lucrezia 2</t>
+          <t>L’albero del riccio</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>trama, prezzo, ISBN</t>
+          <t>trama, età, ISBN</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788836240067 · https://www.ibs.it/x/e/9791222114200</t>
+          <t>https://www.ibs.it/x/e/9788861539808</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Gallucci</t>
+          <t>La Meridiana</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Tu sei importante</t>
+          <t>La Puglia è una favola</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>trama, età, prezzo, ISBN</t>
+          <t>trama, età, ISBN</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788836242580</t>
+          <t>https://www.ibs.it/x/e/9791256260089</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Pelledoca</t>
+          <t>La Meridiana</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Les 3 Moustaches. il Mistero del Tappeto Peloso</t>
+          <t>Milagro in CAA</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>ISBN</t>
+          <t>trama, età, ISBN</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788832791358</t>
+          <t>https://www.ibs.it/x/e/9788861539983 · età indicata da Bottegart</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Pelledoca</t>
+          <t>La Meridiana</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Lupi, Licantropi e Luna Piena</t>
+          <t>Paul Klee pittore musicista</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>ISBN</t>
+          <t>trama, età, ISBN</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788832791273</t>
+          <t>https://www.ibs.it/x/e/9791256260560</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Momo Edizioni</t>
+          <t>Gallucci</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Libera dal ciclo</t>
+          <t>Il mondo di Lucrezia 2</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>trama</t>
+          <t>trama, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>testo fornito da Bottegart</t>
+          <t>https://www.ibs.it/x/e/9788836240067 · https://www.ibs.it/x/e/9791222114200</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Momo Edizioni</t>
+          <t>Gallucci</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>A cosa servono le cose?</t>
+          <t>Tu sei importante</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>età</t>
+          <t>trama, età, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791280298935</t>
+          <t>https://www.ibs.it/x/e/9788836242580</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Momo Edizioni</t>
+          <t>Pelledoca</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Bollicina</t>
+          <t>Les 3 Moustaches. il Mistero del Tappeto Peloso</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>età</t>
+          <t>ISBN</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791280298782</t>
+          <t>https://www.ibs.it/x/e/9788832791358</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Momo Edizioni</t>
+          <t>Pelledoca</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Cambiare il mondo con i libri. L’incredibile storia di Giangiacomo Feltrinelli</t>
+          <t>Lupi, Licantropi e Luna Piena</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>età</t>
+          <t>ISBN</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791280298225</t>
+          <t>https://www.ibs.it/x/e/9788832791273</t>
         </is>
       </c>
     </row>
@@ -3975,17 +5651,17 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Essere tempesta. Vita e morte di Giacomo Matteotti</t>
+          <t>Libera dal ciclo</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>età</t>
+          <t>trama</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791280298522</t>
+          <t>testo fornito da Bottegart</t>
         </is>
       </c>
     </row>
@@ -3997,7 +5673,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Karukinka. La nostra terra</t>
+          <t>A cosa servono le cose?</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -4007,359 +5683,359 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>età indicata da Bottegart</t>
+          <t>https://www.ibs.it/x/e/9791280298935</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>Tunuè</t>
+          <t>Momo Edizioni</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Angelica e il principe orso (in arrivo)</t>
+          <t>Bollicina</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>trama, prezzo, ISBN</t>
+          <t>età</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788867908424</t>
+          <t>https://www.ibs.it/x/e/9791280298782</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Tunuè</t>
+          <t>Momo Edizioni</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>L’Attraversaspecchi, vol. 1 – Fidanzati dell’inverno</t>
+          <t>Cambiare il mondo con i libri. L’incredibile storia di Giangiacomo Feltrinelli</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>trama, prezzo, ISBN</t>
+          <t>età</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788867908721</t>
+          <t>https://www.ibs.it/x/e/9791280298225</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Tunuè</t>
+          <t>Momo Edizioni</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Noi due</t>
+          <t>Essere tempesta. Vita e morte di Giacomo Matteotti</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>trama, prezzo, ISBN</t>
+          <t>età</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788867906895</t>
+          <t>https://www.ibs.it/x/e/9791280298522</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Cronache Ribelli</t>
+          <t>Momo Edizioni</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>C’era una (ri)volta – Quaranta storie da leggere e colorare (vol. I)</t>
+          <t>Karukinka. La nostra terra</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>trama, età, prezzo, ISBN</t>
+          <t>età</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>https://cronacheribelli.it/products/cera-una-rivolta-quaranta-storie-da-leggere-e-colorare</t>
+          <t>età indicata da Bottegart</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Cronache Ribelli</t>
+          <t>Tunuè</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>C’era una (ri)volta – Quaranta storie da leggere e colorare (vol. II)</t>
+          <t>L’Attraversaspecchi, vol. 1 – Fidanzati dell’inverno</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>trama, età, prezzo, ISBN</t>
+          <t>trama, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>https://cronacheribelli.it/products/cera-una-rivolta-volume-ii-quaranta-storie-da-leggere-e-colorare</t>
+          <t>https://www.ibs.it/x/e/9788867908721</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Cronache Ribelli</t>
+          <t>Tunuè</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Laika e i cani venuti dallo spazio</t>
+          <t>Noi due</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>trama, età, prezzo</t>
+          <t>trama, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>https://cronacheribelli.it/products/laika-e-i-cani-venuti-dallo-spazio</t>
+          <t>https://www.ibs.it/x/e/9788867906895</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Dalia Edizioni</t>
+          <t>Cronache Ribelli</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>UVA. Una Vita Altrove</t>
+          <t>C’era una (ri)volta – Quaranta storie da leggere e colorare (vol. I)</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>trama, prezzo, ISBN</t>
+          <t>trama, età, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788899207632</t>
+          <t>https://cronacheribelli.it/products/cera-una-rivolta-quaranta-storie-da-leggere-e-colorare</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Dalia Edizioni</t>
+          <t>Cronache Ribelli</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Loris Wood verso l’isola di plastica</t>
+          <t>C’era una (ri)volta – Quaranta storie da leggere e colorare (vol. II)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>trama, età, ISBN</t>
+          <t>trama, età, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788899207601</t>
+          <t>https://cronacheribelli.it/products/cera-una-rivolta-volume-ii-quaranta-storie-da-leggere-e-colorare</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Edizioni Corsare</t>
+          <t>Cronache Ribelli</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Due detective e mezzo</t>
+          <t>Laika e i cani venuti dallo spazio</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>trama, prezzo, ISBN</t>
+          <t>trama, età, prezzo</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788899136031</t>
+          <t>https://cronacheribelli.it/products/laika-e-i-cani-venuti-dallo-spazio</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Edizioni Corsare</t>
+          <t>Dalia Edizioni</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Pericolo smartphone</t>
+          <t>UVA. Una Vita Altrove</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>trama, prezzo, ISBN</t>
+          <t>trama, età, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788899136277</t>
+          <t>https://www.ibs.it/x/e/9788899207632</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Dalia Edizioni</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Immagina. Crea. Vivi!</t>
+          <t>Loris Wood verso l’isola di plastica</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>trama, età, prezzo, ISBN</t>
+          <t>trama, età, ISBN</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791259794178</t>
+          <t>https://www.ibs.it/x/e/9788899207601</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Edizioni Corsare</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Io non ho paura del lupo</t>
+          <t>Due detective e mezzo</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>trama, età, prezzo, ISBN</t>
+          <t>trama, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791259792280 · età indicata da Bottegart</t>
+          <t>https://www.ibs.it/x/e/9788899136031</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Edizioni Corsare</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Non esistono piccoli antifascisti</t>
+          <t>Pericolo smartphone</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>trama, età, prezzo, ISBN</t>
+          <t>trama, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791259792822 · età indicata da Bottegart</t>
+          <t>https://www.ibs.it/x/e/9788899136277</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Logos</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Edmondo e la Cacca Misteriosa</t>
+          <t>Immagina. Crea. Vivi!</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>trama</t>
+          <t>trama, età, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788857614250</t>
+          <t>https://www.ibs.it/x/e/9791259794178</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Logos</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>La Famiglia Volpitassi 1 – l’Incontro</t>
+          <t>Io non ho paura del lupo</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>trama</t>
+          <t>trama, età, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788857614120</t>
+          <t>https://www.ibs.it/x/e/9791259792280 · età indicata da Bottegart</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Logos</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Pinocchio</t>
+          <t>Non esistono piccoli antifascisti</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>trama</t>
+          <t>trama, età, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788857614502</t>
+          <t>https://www.ibs.it/x/e/9791259792822 · età indicata da Bottegart</t>
         </is>
       </c>
     </row>
@@ -4371,7 +6047,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Cosa Fanno le Bambine?</t>
+          <t>Edmondo e la Cacca Misteriosa</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -4381,7 +6057,7 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788857613949</t>
+          <t>https://www.ibs.it/x/e/9788857614250</t>
         </is>
       </c>
     </row>
@@ -4393,7 +6069,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Bella Bambina Dai Capelli Turchini</t>
+          <t>La Famiglia Volpitassi 1 – l’Incontro</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -4403,7 +6079,7 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788857613628</t>
+          <t>https://www.ibs.it/x/e/9788857614120</t>
         </is>
       </c>
     </row>
@@ -4415,7 +6091,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Cosimo</t>
+          <t>Pinocchio</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -4425,7 +6101,7 @@
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788857607894</t>
+          <t>https://www.ibs.it/x/e/9788857614502</t>
         </is>
       </c>
     </row>
@@ -4437,7 +6113,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Mira</t>
+          <t>Cosa Fanno le Bambine?</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -4447,7 +6123,7 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788857613819</t>
+          <t>https://www.ibs.it/x/e/9788857613949</t>
         </is>
       </c>
     </row>
@@ -4459,7 +6135,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Barbablù</t>
+          <t>Bella Bambina Dai Capelli Turchini</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -4469,7 +6145,7 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788857610047</t>
+          <t>https://www.ibs.it/x/e/9788857613628</t>
         </is>
       </c>
     </row>
@@ -4481,7 +6157,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>La Sirenetta</t>
+          <t>Cosimo</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -4491,73 +6167,73 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788857613604</t>
+          <t>https://www.ibs.it/x/e/9788857607894</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>effequ</t>
+          <t>Logos</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>VIETATO</t>
+          <t>Mira</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>trama, ISBN</t>
+          <t>trama</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>https://www.effequ.it/prodotto/vietato/</t>
+          <t>https://www.ibs.it/x/e/9788857613819</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>effequ</t>
+          <t>Logos</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>Barbablù</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>trama, ISBN</t>
+          <t>trama</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>https://www.effequ.it/prodotto/web/</t>
+          <t>https://www.ibs.it/x/e/9788857610047</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>effequ</t>
+          <t>Logos</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>XY</t>
+          <t>La Sirenetta</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>trama, ISBN</t>
+          <t>trama, età</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9791281639478 · testo fornito da Bottegart</t>
+          <t>https://www.ibs.it/x/e/9788857613604</t>
         </is>
       </c>
     </row>
@@ -4569,7 +6245,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>ZAMPA</t>
+          <t>VIETATO</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -4579,73 +6255,73 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>https://www.effequ.it/prodotto/zampa/</t>
+          <t>https://www.effequ.it/prodotto/vietato/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>BeccoGiallo</t>
+          <t>effequ</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Il bullismo spiegato ai bambini</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>prezzo, ISBN</t>
+          <t>trama, ISBN</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833140254 · https://www.beccogiallo.it/negozio/kids/criticalkids/il-bullismo-spiegato-ai-bambini/</t>
+          <t>https://www.effequ.it/prodotto/web/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>BeccoGiallo</t>
+          <t>effequ</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Il razzismo spiegato ai bambini</t>
+          <t>XY</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>ISBN</t>
+          <t>trama, ISBN</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833140391</t>
+          <t>https://www.ibs.it/x/e/9791281639478 · testo fornito da Bottegart</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>BeccoGiallo</t>
+          <t>effequ</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>La Shoah spiegata alle bambine e ai bambini</t>
+          <t>ZAMPA</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>ISBN</t>
+          <t>trama, ISBN</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833144245</t>
+          <t>https://www.effequ.it/prodotto/zampa/</t>
         </is>
       </c>
     </row>
@@ -4657,17 +6333,17 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>La biodiversità spiegata alle bambine e ai bambini</t>
+          <t>Il bullismo spiegato ai bambini</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>trama, ISBN</t>
+          <t>prezzo, ISBN</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833143415</t>
+          <t>https://www.ibs.it/x/e/9788833140254 · https://www.beccogiallo.it/negozio/kids/criticalkids/il-bullismo-spiegato-ai-bambini/</t>
         </is>
       </c>
     </row>
@@ -4679,7 +6355,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>La sessualità spiegata ai bambini e alle bambine di ieri, oggi e domani</t>
+          <t>Il razzismo spiegato ai bambini</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -4689,7 +6365,7 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833142159</t>
+          <t>https://www.ibs.it/x/e/9788833140391</t>
         </is>
       </c>
     </row>
@@ -4701,7 +6377,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>L’Europa spiegata alle bambine e ai bambini</t>
+          <t>La Shoah spiegata alle bambine e ai bambini</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -4711,7 +6387,7 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833143132</t>
+          <t>https://www.ibs.it/x/e/9788833144245</t>
         </is>
       </c>
     </row>
@@ -4723,17 +6399,17 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>L’immigrazione spiegata ai bambini</t>
+          <t>La biodiversità spiegata alle bambine e ai bambini</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>trama, età, prezzo, ISBN</t>
+          <t>trama, ISBN</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>https://www.beccogiallo.it/negozio/kids/criticalkids/limmigrazione-spiegata-ai-bambini/</t>
+          <t>https://www.ibs.it/x/e/9788833143415</t>
         </is>
       </c>
     </row>
@@ -4745,17 +6421,17 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Paleo Stories – Estinzione</t>
+          <t>La sessualità spiegata ai bambini e alle bambine di ieri, oggi e domani</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>prezzo, ISBN</t>
+          <t>ISBN</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833143620</t>
+          <t>https://www.ibs.it/x/e/9788833142159</t>
         </is>
       </c>
     </row>
@@ -4767,17 +6443,17 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Archeo Tales – Il mito del Minotauro</t>
+          <t>L’Europa spiegata alle bambine e ai bambini</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>trama, età, ISBN</t>
+          <t>ISBN</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833143866</t>
+          <t>https://www.ibs.it/x/e/9788833143132</t>
         </is>
       </c>
     </row>
@@ -4789,7 +6465,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Come l’acqua</t>
+          <t>L’immigrazione spiegata ai bambini</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -4799,7 +6475,7 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833143750</t>
+          <t>https://www.beccogiallo.it/negozio/kids/criticalkids/limmigrazione-spiegata-ai-bambini/</t>
         </is>
       </c>
     </row>
@@ -4811,17 +6487,17 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Figli della foresta. Due vite africane rapite dal colonialismo italiano</t>
+          <t>Paleo Stories – Estinzione</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>trama, età, prezzo, ISBN</t>
+          <t>prezzo, ISBN</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833144320 · https://www.beccogiallo.it/negozio/graphic-journalism/figli-della-foresta/</t>
+          <t>https://www.ibs.it/x/e/9788833143620</t>
         </is>
       </c>
     </row>
@@ -4833,17 +6509,17 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Il cinema spiegato ai bambini e alle bambine</t>
+          <t>Archeo Tales – Il mito del Minotauro</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>trama, età, prezzo, ISBN</t>
+          <t>trama, età, ISBN</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833143552</t>
+          <t>https://www.ibs.it/x/e/9788833143866</t>
         </is>
       </c>
     </row>
@@ -4855,7 +6531,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Il mio corpo!</t>
+          <t>Come l’acqua</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -4865,7 +6541,7 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833143767 · https://www.beccogiallo.it/negozio/kids/illustrati/il-mio-corpo/</t>
+          <t>https://www.ibs.it/x/e/9788833143750</t>
         </is>
       </c>
     </row>
@@ -4877,17 +6553,17 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Il primo soccorso spiegato alle bambine e ai bambini</t>
+          <t>Figli della foresta. Due vite africane rapite dal colonialismo italiano</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>trama, età, ISBN</t>
+          <t>trama, età, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833143965</t>
+          <t>https://www.ibs.it/x/e/9788833144320 · https://www.beccogiallo.it/negozio/graphic-journalism/figli-della-foresta/</t>
         </is>
       </c>
     </row>
@@ -4899,17 +6575,17 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>La Costituzione spiegata ai bambini (Piero e Nilde)</t>
+          <t>Il cinema spiegato ai bambini e alle bambine</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>trama, età, ISBN</t>
+          <t>trama, età, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833141084</t>
+          <t>https://www.ibs.it/x/e/9788833143552</t>
         </is>
       </c>
     </row>
@@ -4921,17 +6597,17 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>La Resistenza spiegata ai bambini</t>
+          <t>Il mio corpo!</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>trama, età, ISBN</t>
+          <t>trama, età, prezzo, ISBN</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833141527</t>
+          <t>https://www.ibs.it/x/e/9788833143767 · https://www.beccogiallo.it/negozio/kids/illustrati/il-mio-corpo/</t>
         </is>
       </c>
     </row>
@@ -4943,7 +6619,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>La disabilità spiegata ai bambini e alle bambine</t>
+          <t>Il primo soccorso spiegato alle bambine e ai bambini</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -4953,7 +6629,7 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833143644</t>
+          <t>https://www.ibs.it/x/e/9788833143965</t>
         </is>
       </c>
     </row>
@@ -4965,7 +6641,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Le emozioni spiegate alle bambine e ai bambini</t>
+          <t>La Costituzione spiegata ai bambini (Piero e Nilde)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -4975,7 +6651,7 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833143958</t>
+          <t>https://www.ibs.it/x/e/9788833141084</t>
         </is>
       </c>
     </row>
@@ -4987,22 +6663,2228 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Woman Power</t>
+          <t>La Resistenza spiegata ai bambini</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>trama, età, prezzo, ISBN</t>
+          <t>trama, età, ISBN</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibs.it/x/e/9788833143460</t>
+          <t>https://www.ibs.it/x/e/9788833141527</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>La disabilità spiegata ai bambini e alle bambine</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>trama, età, ISBN</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ibs.it/x/e/9788833143644</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>Le emozioni spiegate alle bambine e ai bambini</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>trama, età, ISBN</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ibs.it/x/e/9788833143958</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D148"/>
+  <autoFilter ref="A3:D150"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Libri in cui l’età del catalogo dell’editore e quella indicata su IBS differiscono di 2 anni o più. Nel flipbook c’è l’età del catalogo: se preferisci quella di IBS, scrivilo nelle correzioni.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Casa editrice</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Titolo</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Fascia nel flipbook</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Età nel flipbook</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Età su IBS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Minibombo</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Il piccolo fienile rosso</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>da 1 anno</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Minibombo</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>La mia famiglia è uno zoo</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>da 1 anno</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Settenove</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>In famiglia!</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>da 4 anni</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>da 6 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Settenove</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Una damigella NON in pericolo!</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Settenove</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Il primo voto di Matilde</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>da 10 anni</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>da 12 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Biancaneve</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Che rabbia!</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Domino gli aggettivi con i simboli</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Domino i verbi con i simboli</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>I musicanti di Brema</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Il brutto anatroccolo</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Il gatto con gli stivali</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Il lupo e i sette capretti</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Il piccolo coniglio bianco</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Lei ci sarà sempre</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Lindo Porcello</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>da 2 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Ninna nanna per una pecorella</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Piccolo Uovo</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Questo posso farlo</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Raperonzolo</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Una scatola gialla</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>0-6 anni</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Che bambino fortunato!</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>3-9 anni</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>In cielo, ma dove?</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>3-9 anni</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>La bambina che andava a pile</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>3-9 anni</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>La distanza dei pesci</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>3-9 anni</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Le parole di Bianca sono farfalle</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>3-9 anni</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>La vecchia casa sul canale</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Prime letture (6-8)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>6-12 anni</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Lilo</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Prime letture (6-8)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>6-12 anni</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>da 10 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Vi presento Hank 1 – Un segnalibro in cerca d’autore</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Prime letture (6-8)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>6-9 anni</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>da 9 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Farfariel – Il libro di Micù</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>9+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>da 9 anni</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>da 12 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>La più bella nuotata della mia vita</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>9+</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>da 9 anni</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>da 11 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Gabbie</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Scuola media (11-13)</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>da 12 anni</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>da 6 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Mostraci chi sei</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Scuola media (11-13)</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>da 12 anni</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>da 10 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Professor papà</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Scuola media (11-13)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>da 12 anni</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>da 10 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Tutta la rabbia che ho dentro</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Scuola media (11-13)</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>da 12 anni</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>da 10 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Una mamma svitata</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Scuola media (11-13)</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>da 12 anni</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>da 10 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Divergente</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Adolescenza (14+)</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>da 14 anni</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>da 10 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Uovonero</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Il mio posto</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Adolescenza (14+)</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>da 14 anni</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>da 12 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Camelozampa</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Peggy trova tutto</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>0-3 anni</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>da 2 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Pelledoca</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Susan Duckling e il Caso del Regalo di Compleanno</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Prime letture (6-8)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>da 6 anni</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Pelledoca</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Il Mistero del Cadavere Senza Testa</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>da 10 anni</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>da 12 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Tunuè</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Brina. L’alba all’orizzonte</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Prime letture (6-8)</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>da 6 anni</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Tunuè</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Monster Allergy. Collection, vol. 1</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Prime letture (6-8)</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>da 6 anni</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>da 10 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Dalia Edizioni</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Alla scoperta della libertà</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Dalia Edizioni</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Argo e Calypso, cani da biblioteca</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Dalia Edizioni</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Arturo e Nadir</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Dalia Edizioni</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Damian e la Lupa</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Dalia Edizioni</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Il mistero di Pyrgi. Avventura tra gli Etruschi</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Dalia Edizioni</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Il vampiro Cicorione</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Dalia Edizioni</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Slò, la magia della lentezza</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Dalia Edizioni</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Febe e i gatti ruba storie</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>da 10 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Edizioni Corsare</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Igor</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Edizioni Corsare</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>MALdiPAURA</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Edizioni Corsare</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Alieni</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>9+</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>da 9 anni</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Edizioni Corsare</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Viola, la gallina e il soldato</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>9+</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>da 9 anni</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>da 11 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Edizioni Corsare</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>L’estate in cui Ethan salvò San Francisco</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Adolescenza (14+)</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>da 14 anni</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>da 12 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Edizioni Corsare</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Quattro giorni</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Adolescenza (14+)</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>da 14 anni</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>da 10 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Logos</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>La Famiglia Volpitassi 1 – l’Incontro</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>da 6 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Logos</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Pinocchio</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>da 3 anni</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Logos</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Cosa Fanno le Bambine?</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Prime letture (6-8)</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>da 6 anni</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>da 4 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Logos</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Bella Bambina Dai Capelli Turchini</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Logos</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Cosimo</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>da 6 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Logos</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Mira</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Logos</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Barbablù</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Scuola media (11-13)</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>da 12 anni</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Il meraviglioso mago di Oz</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Prime letture (6-8)</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>da 6 anni</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>da 9 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>L’isola del tesoro (ed. MinaLima)</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Prime letture (6-8)</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>da 6 anni</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>da 9 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>20.000 leghe sotto i mari</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>da 10 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Anatomia</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>8-11 anni</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Le tribolazioni del giovane Cosimo</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>da 6 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Sangue d’ontano – La volpe artica</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>9+</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>9-12 anni</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>da 12 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Atlante dei relitti</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Scuola media (11-13)</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>da 11 anni</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Sirene, centauri e altre chimere (L’enciclopedia del meraviglioso)</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Scuola media (11-13)</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>11-13 anni</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Le cronache dell’acero e del ciliegio 1. La maschera di Nō</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Scuola media (11-13)</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>da 11 anni</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>da 13 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>L’Ippocampo</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Le streghe di Venezia</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Scuola media (11-13)</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>11-13 anni</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Il bullismo spiegato ai bambini</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Il razzismo spiegato ai bambini</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>L’Europa spiegata alle bambine e ai bambini</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>3-6 anni</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>da 5 anni</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>da 7 anni</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>BeccoGiallo</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Paleo Stories – Estinzione</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Prime letture (6-8)</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>da 6 anni</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>da 8 anni</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:E81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>